--- a/diseases/d024/2026-2029.xlsx
+++ b/diseases/d024/2026-2029.xlsx
@@ -24444,6 +24444,154 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>3366</v>
+      </c>
+      <c r="O127" t="n">
+        <v>3366</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.2382310451425582</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24477,7 +24625,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -24560,7 +24708,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -24570,7 +24718,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -24622,7 +24770,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19646</v>
+        <v>23012</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d024/2026-2029.xlsx
+++ b/diseases/d024/2026-2029.xlsx
@@ -22162,12 +22162,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -22201,10 +22201,10 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O115" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
@@ -22313,12 +22313,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -22352,10 +22352,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O116" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -22510,7 +22510,7 @@
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
@@ -22547,12 +22547,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -22586,10 +22586,10 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="O117" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -22737,10 +22737,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="O118" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
@@ -22932,12 +22932,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -22971,10 +22971,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O119" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
@@ -23083,12 +23083,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -23122,10 +23122,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O120" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
@@ -23317,12 +23317,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -23356,10 +23356,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c r="O121" t="n">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
@@ -23468,12 +23468,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -23507,10 +23507,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c r="O122" t="n">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -23665,7 +23665,7 @@
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
@@ -23702,12 +23702,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -23741,10 +23741,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="O123" t="n">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
@@ -23853,12 +23853,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -23892,10 +23892,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="O124" t="n">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -24050,7 +24050,7 @@
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
@@ -24087,12 +24087,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -24126,10 +24126,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="O125" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -24277,10 +24277,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
@@ -24472,123 +24472,3203 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>2</v>
+      </c>
+      <c r="O127" t="n">
+        <v>2</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>2</v>
+      </c>
+      <c r="O128" t="n">
+        <v>2</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>D024</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Dysentery</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
         <is>
           <t>细菌性和阿米巴性痢疾</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="K129" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N127" t="n">
+      <c r="N129" t="n">
         <v>3366</v>
       </c>
-      <c r="O127" t="n">
+      <c r="O129" t="n">
         <v>3366</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="Q129" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="n">
+      <c r="R129" t="n">
         <v>0.2382310451425582</v>
       </c>
-      <c r="S127" t="inlineStr">
+      <c r="S129" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO127" t="inlineStr">
+      <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP127" t="inlineStr">
+      <c r="AP129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR127" t="inlineStr">
+      <c r="AR129" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS127" t="inlineStr"/>
-      <c r="AT127" t="n">
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="n">
         <v>0</v>
       </c>
-      <c r="AU127" t="inlineStr">
+      <c r="AU129" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV127" t="inlineStr">
+      <c r="AV129" t="inlineStr">
         <is>
           <t>cdc_weekly</t>
         </is>
       </c>
-      <c r="AW127" t="inlineStr">
+      <c r="AW129" t="inlineStr">
         <is>
           <t>China CDC Weekly</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
+      <c r="AX129" t="inlineStr">
         <is>
           <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
-      <c r="AY127" t="inlineStr">
+      <c r="AY129" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
+      <c r="AZ129" t="inlineStr">
         <is>
           <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
-      <c r="BA127" t="inlineStr">
+      <c r="BA129" t="inlineStr">
         <is>
           <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
-      <c r="BB127" t="inlineStr">
+      <c r="BB129" t="inlineStr">
         <is>
           <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
-      <c r="BC127" t="inlineStr">
+      <c r="BC129" t="inlineStr">
         <is>
           <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>CN-CQ</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Chongqing, China</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>68</v>
+      </c>
+      <c r="O130" t="n">
+        <v>68</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>CN-CQ</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Chongqing, China</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>68</v>
+      </c>
+      <c r="O131" t="n">
+        <v>68</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:CN-CQ:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>CN-GD</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>46</v>
+      </c>
+      <c r="O132" t="n">
+        <v>46</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>CN-GD</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>46</v>
+      </c>
+      <c r="O133" t="n">
+        <v>46</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:CN-GD:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>46</v>
+      </c>
+      <c r="O134" t="n">
+        <v>46</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>46</v>
+      </c>
+      <c r="O135" t="n">
+        <v>46</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>29</v>
+      </c>
+      <c r="O136" t="n">
+        <v>29</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>29</v>
+      </c>
+      <c r="O137" t="n">
+        <v>29</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>201</v>
+      </c>
+      <c r="O138" t="n">
+        <v>201</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>201</v>
+      </c>
+      <c r="O139" t="n">
+        <v>201</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>345</v>
+      </c>
+      <c r="O140" t="n">
+        <v>345</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>345</v>
+      </c>
+      <c r="O141" t="n">
+        <v>345</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" t="n">
+        <v>2</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>dysentery</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D024</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Dysentery</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="n">
+        <v>2</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>细菌性和阿米巴性痢疾</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_DYSENTERY; SER_CN_PROV_REPORT_DYSENTERY</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -24708,7 +27788,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -24718,7 +27798,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -24738,7 +27818,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -24770,7 +27850,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23012</v>
+        <v>23763</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d024/2026-2029.xlsx
+++ b/diseases/d024/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4389,6 +4394,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8002,6 +8012,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11230,6 +11245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14458,6 +14478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18071,6 +18096,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21299,6 +21329,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24910,6 +24945,11 @@
       <c r="S129" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
